--- a/docs/data/raw/2026-06-10_HV.xlsx
+++ b/docs/data/raw/2026-06-10_HV.xlsx
@@ -1699,34 +1699,38 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>YIU CHEUNG VICTORY</t>
+          <t>YIU CHEUNG VICTORY(Scratched)</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>P N Wong (-7)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>C H Yip</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>14/10/3/5/8/7</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="P22" t="n">
         <v>20</v>
       </c>
@@ -16752,34 +16756,38 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>YIU CHEUNG VICTORY</t>
+          <t>YIU CHEUNG VICTORY(Scratched)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>P N Wong (-7)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C H Yip</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14/10/3/5/8/7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K10" t="n">
         <v>20</v>
       </c>
@@ -16787,7 +16795,7 @@
         <v>12</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11">
